--- a/docs/kanji_n5.xlsx
+++ b/docs/kanji_n5.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IG24-253\Documents\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3EC421-9DAF-4F5E-869C-DC13FE154E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6850"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kanji_N5" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Kanji</t>
   </si>
@@ -173,23 +174,104 @@
   <si>
     <t>n5_inside.webp</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雪</t>
+  </si>
+  <si>
+    <t>夏</t>
+  </si>
+  <si>
+    <t>秋</t>
+  </si>
+  <si>
+    <t>冬</t>
+  </si>
+  <si>
+    <t>公園</t>
+  </si>
+  <si>
+    <t>街</t>
+  </si>
+  <si>
+    <t>海</t>
+  </si>
+  <si>
+    <t>川</t>
+  </si>
+  <si>
+    <t>家</t>
+  </si>
+  <si>
+    <t>ゆき</t>
+  </si>
+  <si>
+    <t>なつ</t>
+  </si>
+  <si>
+    <t>あき</t>
+  </si>
+  <si>
+    <t>ふゆ</t>
+  </si>
+  <si>
+    <t>こうえん</t>
+  </si>
+  <si>
+    <t>まち</t>
+  </si>
+  <si>
+    <t>うみ</t>
+  </si>
+  <si>
+    <t>かわ</t>
+  </si>
+  <si>
+    <t>いえ</t>
+  </si>
+  <si>
+    <t>snow</t>
+  </si>
+  <si>
+    <t>summer</t>
+  </si>
+  <si>
+    <t>autumn/fall</t>
+  </si>
+  <si>
+    <t>winter</t>
+  </si>
+  <si>
+    <t>park</t>
+  </si>
+  <si>
+    <t>city/town</t>
+  </si>
+  <si>
+    <t>sea</t>
+  </si>
+  <si>
+    <t>river</t>
+  </si>
+  <si>
+    <t>house</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -222,7 +304,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -521,9 +603,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -531,7 +613,7 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -545,7 +627,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -559,7 +641,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -573,7 +655,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -587,7 +669,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -601,7 +683,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -615,7 +697,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -629,7 +711,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -643,7 +725,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="28.8">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -657,7 +739,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -671,7 +753,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -683,6 +765,105 @@
       </c>
       <c r="D11" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/docs/kanji_n5.xlsx
+++ b/docs/kanji_n5.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kanji_N5" sheetId="1" r:id="R3308baa6c3054f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kanji_N5" sheetId="1" r:id="R7a35f27ca2134617"/>
   </x:sheets>
 </x:workbook>
 </file>
